--- a/data/trans_bre/P16A07-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A07-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,22</t>
+          <t>0,77; 5,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,13</t>
+          <t>4,77; 9,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 9,14</t>
+          <t>4,51; 9,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,16</t>
+          <t>-0,26; 3,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,32; 237,44</t>
+          <t>16,48; 230,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>136,91; 570,63</t>
+          <t>128,66; 517,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>156,07; 774,87</t>
+          <t>153,82; 799,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 117,96</t>
+          <t>-4,85; 109,31</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,1</t>
+          <t>2,31; 6,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,67</t>
+          <t>2,63; 6,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,41</t>
+          <t>3,69; 7,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,29</t>
+          <t>2,87; 6,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>70,14; 388,01</t>
+          <t>74,72; 388,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,33; 243,35</t>
+          <t>56,87; 242,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>155,0; 659,58</t>
+          <t>154,51; 628,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,26; 550,09</t>
+          <t>90,18; 505,73</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,42</t>
+          <t>2,36; 6,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,18</t>
+          <t>2,8; 7,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,53</t>
+          <t>1,56; 5,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,8</t>
+          <t>-1,09; 6,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>106,22; 773,99</t>
+          <t>95,17; 701,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,44; 598,37</t>
+          <t>73,14; 633,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,79; 401,57</t>
+          <t>42,68; 380,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 221,76</t>
+          <t>-12,44; 224,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,25</t>
+          <t>3,55; 7,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,62</t>
+          <t>2,37; 6,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,24</t>
+          <t>2,19; 6,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,81</t>
+          <t>2,74; 6,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>143,69; 597,13</t>
+          <t>132,74; 557,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,52; 216,87</t>
+          <t>44,86; 235,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,07; 280,31</t>
+          <t>54,3; 281,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,28; 247,11</t>
+          <t>57,89; 242,94</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,34</t>
+          <t>3,38; 5,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,26</t>
+          <t>4,08; 6,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,94</t>
+          <t>3,92; 6,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,04</t>
+          <t>2,51; 5,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>130,75; 301,93</t>
+          <t>131,42; 291,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>107,3; 230,64</t>
+          <t>109,6; 236,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>155,29; 331,8</t>
+          <t>147,97; 327,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>65,87; 187,79</t>
+          <t>73,01; 191,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A07-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A07-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,3</t>
+          <t>0,81; 5,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,6</t>
+          <t>4,79; 10,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,16</t>
+          <t>4,34; 9,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,94</t>
+          <t>-0,38; 4,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,48; 230,21</t>
+          <t>15,75; 231,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>128,66; 517,31</t>
+          <t>134,23; 602,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>153,82; 799,61</t>
+          <t>152,03; 777,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 109,31</t>
+          <t>-6,64; 112,29</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>216,88%</t>
+          <t>152,68%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,16</t>
+          <t>2,26; 6,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,72</t>
+          <t>2,44; 6,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,35</t>
+          <t>3,68; 7,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,28</t>
+          <t>2,3; 5,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>74,72; 388,97</t>
+          <t>72,66; 388,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,87; 242,8</t>
+          <t>50,25; 235,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>154,51; 628,88</t>
+          <t>148,9; 613,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,18; 505,73</t>
+          <t>64,87; 297,79</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>4,95</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>148,51%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,24</t>
+          <t>2,4; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,41</t>
+          <t>2,56; 7,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,4</t>
+          <t>1,52; 5,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 6,01</t>
+          <t>2,9; 7,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95,17; 701,48</t>
+          <t>103,23; 753,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>73,14; 633,6</t>
+          <t>71,69; 588,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,68; 380,66</t>
+          <t>47,5; 419,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 224,87</t>
+          <t>60,19; 294,38</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>5,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>138,21%</t>
+          <t>158,48%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,13</t>
+          <t>3,53; 7,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,94</t>
+          <t>2,37; 6,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,32</t>
+          <t>2,38; 6,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,84</t>
+          <t>3,82; 7,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>132,74; 557,46</t>
+          <t>143,18; 588,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,86; 235,64</t>
+          <t>44,01; 222,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,3; 281,28</t>
+          <t>59,28; 268,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,89; 242,94</t>
+          <t>86,04; 265,87</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>121,83%</t>
+          <t>122,45%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,25</t>
+          <t>3,29; 5,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,39</t>
+          <t>4,01; 6,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,09</t>
+          <t>3,9; 5,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,12</t>
+          <t>3,26; 5,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>131,42; 291,01</t>
+          <t>125,11; 288,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>109,6; 236,2</t>
+          <t>109,06; 236,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>147,97; 327,52</t>
+          <t>151,89; 324,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,01; 191,07</t>
+          <t>81,58; 168,06</t>
         </is>
       </c>
     </row>
